--- a/public/templates/catalog-import-05.xlsx
+++ b/public/templates/catalog-import-05.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rfdc6bfd1c9fe4981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_过渡接头" sheetId="2" r:id="Recdc0383181b4ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="Rff2eb2603951417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R96227b8fd4864764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rc452e8e9bb1e42b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_过渡接头" sheetId="2" r:id="R0d5d8132977b48bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="Rae42d2e2ef624e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Rd9224515a8ad465b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>

--- a/public/templates/catalog-import-05.xlsx
+++ b/public/templates/catalog-import-05.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rc452e8e9bb1e42b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_过渡接头" sheetId="2" r:id="R0d5d8132977b48bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="Rae42d2e2ef624e8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Rd9224515a8ad465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rb36630a11dbb423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_过渡接头" sheetId="2" r:id="Rf12427c253cd411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="Rd3935d774a234e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R0db8da41ecc04877"/>
   </x:sheets>
 </x:workbook>
 </file>
